--- a/reports/集团总公司_现金流量表_2026-03.xlsx
+++ b/reports/集团总公司_现金流量表_2026-03.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>200850000</v>
+        <v>196642729</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>554346000</v>
+        <v>544935631</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4027151</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>11072233</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1994670</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>5523395</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1007223</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2773452</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>798348</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2206026</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>603392</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1665572</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>400124</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1102783</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>300816</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>832364</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>200700</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>552042</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>499806</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1384898</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>252840</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>695036</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>158593</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>439347</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>545900</v>
+        <v>538680</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1506684</v>
+        <v>1482313</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3708000</v>
+        <v>3627560</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>10234080</v>
+        <v>10031996</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>205103900</v>
+        <v>211052632</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>123600000</v>
+        <v>121293061</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>341136000</v>
+        <v>335984410</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1340562</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3685170</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>998090</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2765713</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>671438</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1846681</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>498652</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1380012</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>335639</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>924890</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>250918</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>692760</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>24926000</v>
+        <v>24515815</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>68795760</v>
+        <v>67729494</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11536000</v>
+        <v>11314984</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>31839360</v>
+        <v>31161314</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5253000</v>
+        <v>5150684</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>14498280</v>
+        <v>14260700</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>165315000</v>
+        <v>166369843</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>39788900</v>
+        <v>44682789</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>243818</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>741600</v>
+        <v>731533</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2124950</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>6489000</v>
+        <v>6391676</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1296508</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3955200</v>
+        <v>3875713</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2368768</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20258072</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>61800000</v>
+        <v>60519089</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2910323</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>8961000</v>
+        <v>8765081</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14406628</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>43878000</v>
+        <v>43084145</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>526797</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1606800</v>
+        <v>1583330</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20784869</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18416101</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4740091</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>14523000</v>
+        <v>14279612</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7552142</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>23175000</v>
+        <v>22721104</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7625035</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>23175000</v>
+        <v>22836555</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>242086</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>741600</v>
+        <v>726527</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12534319</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6168806</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>18849000</v>
+        <v>18464672</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6171218</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>18849000</v>
+        <v>18574358</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1014190</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3090000</v>
+        <v>3030554</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>884418</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2688300</v>
+        <v>2642555</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>125874</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>386250</v>
+        <v>378934</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7308870</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5225449</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>26434950</v>
+        <v>31492137</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>26434950</v>
+        <v>31492137</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
